--- a/output/pdf_financials_xlsx/QYOU.xlsx
+++ b/output/pdf_financials_xlsx/QYOU.xlsx
@@ -4539,31 +4539,31 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.108425</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.047183</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.028833</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.093524</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.120235</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.052341</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.03431</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.121817</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.13347</v>
       </c>
     </row>
     <row r="92">
@@ -4594,7 +4594,7 @@
         <v>6.607924</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.701263</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -8496,7 +8496,11 @@
           <t>Foreign exchange translation reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -10826,7 +10830,11 @@
           <t>Foreign exchange translation reserve</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13770,7 +13778,11 @@
           <t>Foreign exchange translation reserve 120,235</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -15102,7 +15114,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -16228,7 +16244,11 @@
           <t>Foreign exchange translation reserve</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QYOU.xlsx
+++ b/output/pdf_financials_xlsx/QYOU.xlsx
@@ -2007,37 +2007,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.218346</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.131086</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.445791</v>
+        <v>1.802694</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.582966</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.069248</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.305095</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.063504</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>9.026915000000001</v>
+        <v>6.54889</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.510951</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.736713</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.946784</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0</v>
@@ -2093,37 +2093,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.218346</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.131086</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.445791</v>
+        <v>1.802694</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.582966</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.069248</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.305095</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.063504</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>9.026915000000001</v>
+        <v>6.54889</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.510951</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.736713</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.946784</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
@@ -2615,31 +2615,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.643821</v>
+        <v>0.286918</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.579568</v>
+        <v>0.996602</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.461079</v>
+        <v>1.391831</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.512498</v>
+        <v>2.207403</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.567576</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.22103</v>
+        <v>4.699055</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>11.48838</v>
+        <v>7.977429</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.270148</v>
+        <v>4.533435</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>8.896718</v>
+        <v>7.949934</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>12.266982</v>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E227" s="5" t="n">

--- a/output/pdf_financials_xlsx/QYOU.xlsx
+++ b/output/pdf_financials_xlsx/QYOU.xlsx
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.230142</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -41686,7 +41686,11 @@
           <t>Loss on disposal of property and equipment (note 7) - -</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E471" s="5" t="n">
         <v>0.398936</v>
       </c>
@@ -42212,7 +42216,11 @@
           <t>Proceeds on disposal of property and equipment (note 7) - -</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E478" s="5" t="n">
         <v>0.230142</v>
       </c>
